--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-04-2026.xlsx
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£51.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>£26.63</t>
+          <t>£32.32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>£32.37</t>
+          <t>£39.75</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£35.65</t>
+          <t>£43.32</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>£40.59</t>
+          <t>£50.31</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>£1484.48</t>
+          <t>£1452.96</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>£1669.60</t>
+          <t>£1634.08</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
